--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.883495145631068</v>
+        <v>0.8932038834951457</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8303571428571429</v>
       </c>
       <c r="E14" t="n">
         <v>0.8613861386138614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8651139145811145</v>
+        <v>0.8678862757776199</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6829545454545455</v>
+        <v>0.6609848484848485</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6282608695652174</v>
+        <v>0.6032608695652174</v>
       </c>
       <c r="E15" t="n">
         <v>0.5608614232209738</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6026345941755687</v>
+        <v>0.6005075545485291</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.717032967032967</v>
+        <v>0.7083655083655084</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5380952380952381</v>
+        <v>0.6026070763500931</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6536082474226804</v>
+        <v>0.6236958443854996</v>
       </c>
       <c r="E16" t="n">
         <v>0.5730676328502415</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6204510213502817</v>
+        <v>0.6269340154878357</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8708524485223516</v>
+        <v>0.8729167447614049</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8273932253313697</v>
+        <v>0.8485016030255909</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8166421207658321</v>
+        <v>0.8029682960717445</v>
       </c>
       <c r="E17" t="n">
         <v>0.840543836992395</v>
       </c>
       <c r="F17" t="n">
-        <v>0.838857907902987</v>
+        <v>0.8412326202127838</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7768939393939394</v>
+        <v>0.7757575757575758</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6369047619047619</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.7279891304347826</v>
       </c>
       <c r="E18" t="n">
         <v>0.7598314606741573</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7351130270356577</v>
+        <v>0.7251207321928194</v>
       </c>
     </row>
     <row r="19">
@@ -863,17 +863,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[85, 3], [9, 6]]</t>
+          <t>[[87, 1], [10, 5]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84, 0], [12, 1]]</t>
+          <t>[[84, 0], [11, 2]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[88, 4], [14, 6]]</t>
+          <t>[[88, 4], [15, 5]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 3], [11, 4]]</t>
+          <t>[[86, 2], [12, 4]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8651139145811145</v>
+        <v>0.8678862757776199</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01690958921471686</v>
+        <v>0.02470726193841993</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6026345941755687</v>
+        <v>0.6005075545485291</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05694554296668258</v>
+        <v>0.03805629757197986</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6204510213502817</v>
+        <v>0.6269340154878357</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06974083168052773</v>
+        <v>0.05033627154112032</v>
       </c>
       <c r="L4" t="n">
-        <v>0.838857907902987</v>
+        <v>0.8412326202127838</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02031916048296535</v>
+        <v>0.02510654687447396</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7351130270356577</v>
+        <v>0.7251207321928194</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05369169634053752</v>
+        <v>0.05375688262967989</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[86, 3], [11, 4]]</t>
+          <t>[[86, 2], [12, 4]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7572815533980582</v>
+        <v>0.8932038834951457</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.9175257731958762</v>
       </c>
       <c r="D8" t="n">
         <v>0.8482142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8316831683168316</v>
+        <v>0.8415841584158416</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8283669168057475</v>
+        <v>0.8751320252052872</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8303030303030303</v>
+        <v>0.8268939393939394</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8310439560439561</v>
+        <v>0.8548534798534799</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8489130434782608</v>
+        <v>0.8293478260869566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8323970037453183</v>
+        <v>0.8019662921348314</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8356642583926412</v>
+        <v>0.8282653843673018</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6824515969909977</v>
+        <v>0.8015414258188824</v>
       </c>
       <c r="C10" t="n">
-        <v>0.775462962962963</v>
+        <v>0.8330464716006885</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7842003853564548</v>
+        <v>0.7779591836734694</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7187551187551188</v>
+        <v>0.7170868347338936</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7402175160163836</v>
+        <v>0.7824084789567335</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7917033333453062</v>
+        <v>0.897132274538414</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8855956471935853</v>
+        <v>0.9199744486044324</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8597577759427469</v>
+        <v>0.8582507288629737</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8546216783840546</v>
+        <v>0.8601658485176249</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8479196087164232</v>
+        <v>0.8838808251308613</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9363636363636364</v>
+        <v>0.9454545454545454</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9184981684981686</v>
+        <v>0.9102564102564102</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9298913043478261</v>
+        <v>0.9364130434782609</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8895131086142323</v>
+        <v>0.8838951310861423</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9185665544559658</v>
+        <v>0.9190047825688398</v>
       </c>
     </row>
     <row r="13">
@@ -721,27 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[64, 24], [1, 14]]</t>
+          <t>[[81, 7], [4, 11]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[75, 9], [3, 10]]</t>
+          <t>[[79, 5], [3, 10]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[78, 14], [3, 17]]</t>
+          <t>[[79, 13], [4, 16]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[74, 15], [2, 10]]</t>
+          <t>[[76, 13], [3, 9]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[73, 16], [2, 13]]</t>
+          <t>[[79, 10], [4, 12]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8283669168057475</v>
+        <v>0.8751320252052872</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04402992709082643</v>
+        <v>0.03151922427728081</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8356642583926412</v>
+        <v>0.8282653843673018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007685948536086601</v>
+        <v>0.01871911867066343</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7402175160163836</v>
+        <v>0.7824084789567335</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04175604813346717</v>
+        <v>0.04247643283967006</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8479196087164232</v>
+        <v>0.8838808251308613</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03451381402077307</v>
+        <v>0.02596946532622683</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9185665544559658</v>
+        <v>0.9190047825688398</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01795197396151251</v>
+        <v>0.02404089822549222</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[73, 16], [2, 13]]</t>
+          <t>[[79, 10], [4, 12]]</t>
         </is>
       </c>
     </row>
